--- a/public/templates/DentalIntra_Template.xlsx
+++ b/public/templates/DentalIntra_Template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Dental Intra" sheetId="1" r:id="rId1"/>
+    <sheet name="Dental Intra Import" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N48"/>
+  <dimension ref="A1:R46"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -413,6 +413,10 @@
     <col min="12" max="12" width="18.83203125" customWidth="1"/>
     <col min="13" max="13" width="18.83203125" customWidth="1"/>
     <col min="14" max="14" width="18.83203125" customWidth="1"/>
+    <col min="15" max="15" width="18.83203125" customWidth="1"/>
+    <col min="16" max="16" width="18.83203125" customWidth="1"/>
+    <col min="17" max="17" width="18.83203125" customWidth="1"/>
+    <col min="18" max="18" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -583,7 +587,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>TEST: LINEARITY OF mAs LOADING</v>
+        <v>TEST: LINEARITY OF TIME</v>
       </c>
     </row>
     <row r="18">
@@ -594,15 +598,18 @@
         <v>kV</v>
       </c>
       <c r="C18" t="str">
-        <v>mAs Range</v>
+        <v>mA</v>
       </c>
       <c r="D18" t="str">
+        <v>Time Station (sec)</v>
+      </c>
+      <c r="E18" t="str">
         <v>Measured mR 1</v>
       </c>
-      <c r="E18" t="str">
+      <c r="F18" t="str">
         <v>Measured mR 2</v>
       </c>
-      <c r="F18" t="str">
+      <c r="G18" t="str">
         <v>Measured mR 3</v>
       </c>
     </row>
@@ -614,16 +621,19 @@
         <v>80</v>
       </c>
       <c r="C19" t="str">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="D19" t="str">
-        <v>4.1</v>
+        <v>0.1</v>
       </c>
       <c r="E19" t="str">
-        <v>4.2</v>
+        <v>10.1</v>
       </c>
       <c r="F19" t="str">
-        <v>4.1</v>
+        <v>10.2</v>
+      </c>
+      <c r="G19" t="str">
+        <v>10.1</v>
       </c>
     </row>
     <row r="20">
@@ -634,100 +644,109 @@
         <v>80</v>
       </c>
       <c r="C20" t="str">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="D20" t="str">
-        <v>8.1</v>
+        <v>0.2</v>
       </c>
       <c r="E20" t="str">
-        <v>8.2</v>
+        <v>20.1</v>
       </c>
       <c r="F20" t="str">
-        <v>8.1</v>
+        <v>20.2</v>
+      </c>
+      <c r="G20" t="str">
+        <v>20.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>100</v>
+        <v>Tolerance Operator</v>
       </c>
       <c r="B21" t="str">
-        <v>80</v>
-      </c>
-      <c r="C21" t="str">
-        <v>20</v>
-      </c>
-      <c r="D21" t="str">
-        <v>16.1</v>
-      </c>
-      <c r="E21" t="str">
-        <v>16.2</v>
-      </c>
-      <c r="F21" t="str">
-        <v>16.1</v>
+        <v>&lt;=</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>100</v>
+        <v>Tolerance Value (CoL)</v>
       </c>
       <c r="B22" t="str">
-        <v>80</v>
-      </c>
-      <c r="C22" t="str">
-        <v>50</v>
-      </c>
-      <c r="D22" t="str">
-        <v>40.1</v>
-      </c>
-      <c r="E22" t="str">
-        <v>40.2</v>
-      </c>
-      <c r="F22" t="str">
-        <v>40.1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>Tolerance Operator</v>
-      </c>
-      <c r="B23" t="str">
-        <v>&lt;=</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Tolerance Value (CoL)</v>
-      </c>
-      <c r="B24" t="str">
-        <v>0.1</v>
+        <v>TEST: LINEARITY OF mA LOADING</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>FDD (cm)</v>
+      </c>
+      <c r="B25" t="str">
+        <v>kV</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Time</v>
+      </c>
+      <c r="D25" t="str">
+        <v>mA Station</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Measured mR 1</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Measured mR 2</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Measured mR 3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>TEST: LINEARITY OF mA LOADING</v>
+        <v>100</v>
+      </c>
+      <c r="B26" t="str">
+        <v>80</v>
+      </c>
+      <c r="C26" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="D26" t="str">
+        <v>50</v>
+      </c>
+      <c r="E26" t="str">
+        <v>5.1</v>
+      </c>
+      <c r="F26" t="str">
+        <v>5.2</v>
+      </c>
+      <c r="G26" t="str">
+        <v>5.1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>FDD (cm)</v>
+        <v>100</v>
       </c>
       <c r="B27" t="str">
-        <v>kV</v>
+        <v>80</v>
       </c>
       <c r="C27" t="str">
-        <v>Time</v>
+        <v>0.5</v>
       </c>
       <c r="D27" t="str">
-        <v>mA Station</v>
+        <v>100</v>
       </c>
       <c r="E27" t="str">
-        <v>Measured mR 1</v>
+        <v>10.1</v>
       </c>
       <c r="F27" t="str">
-        <v>Measured mR 2</v>
+        <v>10.2</v>
       </c>
       <c r="G27" t="str">
-        <v>Measured mR 3</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="28">
@@ -741,16 +760,16 @@
         <v>0.5</v>
       </c>
       <c r="D28" t="str">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="E28" t="str">
-        <v>5.1</v>
+        <v>20.1</v>
       </c>
       <c r="F28" t="str">
-        <v>5.2</v>
+        <v>20.2</v>
       </c>
       <c r="G28" t="str">
-        <v>5.1</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="29">
@@ -764,302 +783,292 @@
         <v>0.5</v>
       </c>
       <c r="D29" t="str">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E29" t="str">
-        <v>10.1</v>
+        <v>30.1</v>
       </c>
       <c r="F29" t="str">
-        <v>10.2</v>
+        <v>30.2</v>
       </c>
       <c r="G29" t="str">
-        <v>10.1</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>100</v>
+        <v>Tolerance Operator</v>
       </c>
       <c r="B30" t="str">
-        <v>80</v>
-      </c>
-      <c r="C30" t="str">
-        <v>0.5</v>
-      </c>
-      <c r="D30" t="str">
-        <v>200</v>
-      </c>
-      <c r="E30" t="str">
-        <v>20.1</v>
-      </c>
-      <c r="F30" t="str">
-        <v>20.2</v>
-      </c>
-      <c r="G30" t="str">
-        <v>20.1</v>
+        <v>&lt;=</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>100</v>
+        <v>Tolerance Value (CoL)</v>
       </c>
       <c r="B31" t="str">
-        <v>80</v>
-      </c>
-      <c r="C31" t="str">
-        <v>0.5</v>
-      </c>
-      <c r="D31" t="str">
-        <v>300</v>
-      </c>
-      <c r="E31" t="str">
-        <v>30.1</v>
-      </c>
-      <c r="F31" t="str">
-        <v>30.2</v>
-      </c>
-      <c r="G31" t="str">
-        <v>30.1</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>Tolerance Operator</v>
-      </c>
-      <c r="B32" t="str">
-        <v>&lt;=</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Tolerance Value (CoL)</v>
-      </c>
-      <c r="B33" t="str">
-        <v>0.1</v>
+        <v>TEST: CONSISTENCY OF RADIATION OUTPUT</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Tolerance Operator</v>
+      </c>
+      <c r="B34" t="str">
+        <v>&lt;=</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>TEST: CONSISTENCY OF RADIATION OUTPUT</v>
+        <v>Tolerance Value (CoV)</v>
+      </c>
+      <c r="B35" t="str">
+        <v>0.05</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Tolerance Operator</v>
+        <v>FFD</v>
       </c>
       <c r="B36" t="str">
-        <v>&lt;=</v>
+        <v>Test kV</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Test mAs</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Meas 1</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Meas 2</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Meas 3</v>
+      </c>
+      <c r="G36" t="str">
+        <v>Mean</v>
+      </c>
+      <c r="H36" t="str">
+        <v>CoV</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Tolerance Value (CoV)</v>
+        <v>40</v>
       </c>
       <c r="B37" t="str">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v>FDD (cm)</v>
-      </c>
-      <c r="B38" t="str">
-        <v>Test kV</v>
-      </c>
-      <c r="C38" t="str">
-        <v>Test mAs</v>
-      </c>
-      <c r="D38" t="str">
-        <v>Meas 1</v>
-      </c>
-      <c r="E38" t="str">
-        <v>Meas 2</v>
-      </c>
-      <c r="F38" t="str">
-        <v>Meas 3</v>
+        <v>120</v>
+      </c>
+      <c r="C37" t="str">
+        <v>100</v>
+      </c>
+      <c r="D37" t="str">
+        <v>50.1</v>
+      </c>
+      <c r="E37" t="str">
+        <v>50.2</v>
+      </c>
+      <c r="F37" t="str">
+        <v>50.1</v>
+      </c>
+      <c r="G37" t="str">
+        <v>50.13</v>
+      </c>
+      <c r="H37" t="str">
+        <v>0.01</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>40</v>
-      </c>
-      <c r="B39" t="str">
-        <v>120</v>
-      </c>
-      <c r="C39" t="str">
-        <v>100</v>
-      </c>
-      <c r="D39" t="str">
-        <v>50.1</v>
-      </c>
-      <c r="E39" t="str">
-        <v>50.2</v>
-      </c>
-      <c r="F39" t="str">
-        <v>50.1</v>
+        <v>TEST: RADIATION LEAKAGE LEVEL</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Distance</v>
+      </c>
+      <c r="B40" t="str">
+        <v>kV</v>
+      </c>
+      <c r="C40" t="str">
+        <v>mA</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Time</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Location</v>
+      </c>
+      <c r="F40" t="str">
+        <v>Front</v>
+      </c>
+      <c r="G40" t="str">
+        <v>Back</v>
+      </c>
+      <c r="H40" t="str">
+        <v>Left</v>
+      </c>
+      <c r="I40" t="str">
+        <v>Right</v>
+      </c>
+      <c r="J40" t="str">
+        <v>Top</v>
+      </c>
+      <c r="K40" t="str">
+        <v>Max</v>
+      </c>
+      <c r="L40" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="M40" t="str">
+        <v>Remark</v>
+      </c>
+      <c r="N40" t="str">
+        <v>Workload</v>
+      </c>
+      <c r="O40" t="str">
+        <v>Workload Unit</v>
+      </c>
+      <c r="P40" t="str">
+        <v>Tolerance Value</v>
+      </c>
+      <c r="Q40" t="str">
+        <v>Tolerance Operator</v>
+      </c>
+      <c r="R40" t="str">
+        <v>Tolerance Time</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>TEST: RADIATION LEAKAGE LEVEL</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <v>Distance</v>
-      </c>
-      <c r="B42" t="str">
-        <v>kV</v>
-      </c>
-      <c r="C42" t="str">
-        <v>mA</v>
-      </c>
-      <c r="D42" t="str">
-        <v>Time</v>
-      </c>
-      <c r="E42" t="str">
-        <v>Workload</v>
-      </c>
-      <c r="F42" t="str">
-        <v>Tolerance Value</v>
-      </c>
-      <c r="G42" t="str">
-        <v>Tolerance Operator</v>
-      </c>
-      <c r="H42" t="str">
-        <v>Tolerance Time</v>
-      </c>
-      <c r="I42" t="str">
-        <v>Location</v>
-      </c>
-      <c r="J42" t="str">
-        <v>Front</v>
-      </c>
-      <c r="K42" t="str">
-        <v>Back</v>
-      </c>
-      <c r="L42" t="str">
-        <v>Left</v>
-      </c>
-      <c r="M42" t="str">
-        <v>Right</v>
-      </c>
-      <c r="N42" t="str">
-        <v>Top</v>
+        <v>100</v>
+      </c>
+      <c r="B41" t="str">
+        <v>120</v>
+      </c>
+      <c r="C41" t="str">
+        <v>100</v>
+      </c>
+      <c r="D41" t="str">
+        <v>1</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Tube</v>
+      </c>
+      <c r="F41" t="str">
+        <v>0.01</v>
+      </c>
+      <c r="G41" t="str">
+        <v>0.02</v>
+      </c>
+      <c r="H41" t="str">
+        <v>0.01</v>
+      </c>
+      <c r="I41" t="str">
+        <v>0.01</v>
+      </c>
+      <c r="J41" t="str">
+        <v>0.02</v>
+      </c>
+      <c r="K41" t="str">
+        <v>0.02</v>
+      </c>
+      <c r="L41" t="str">
+        <v>mR/h</v>
+      </c>
+      <c r="M41" t="str">
+        <v/>
+      </c>
+      <c r="N41" t="str">
+        <v>500</v>
+      </c>
+      <c r="O41" t="str">
+        <v>mA in one hour</v>
+      </c>
+      <c r="P41" t="str">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="str">
+        <v>&lt;=</v>
+      </c>
+      <c r="R41" t="str">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>100</v>
-      </c>
-      <c r="B43" t="str">
-        <v>120</v>
-      </c>
-      <c r="C43" t="str">
-        <v>100</v>
-      </c>
-      <c r="D43" t="str">
-        <v>1</v>
-      </c>
-      <c r="E43" t="str">
-        <v>500</v>
-      </c>
-      <c r="F43" t="str">
-        <v>1</v>
-      </c>
-      <c r="G43" t="str">
-        <v>&lt;=</v>
-      </c>
-      <c r="H43" t="str">
-        <v>1</v>
-      </c>
-      <c r="I43" t="str">
-        <v>Tube</v>
-      </c>
-      <c r="J43" t="str">
-        <v>0.01</v>
-      </c>
-      <c r="K43" t="str">
-        <v>0.02</v>
-      </c>
-      <c r="L43" t="str">
-        <v>0.01</v>
-      </c>
-      <c r="M43" t="str">
-        <v>0.01</v>
-      </c>
-      <c r="N43" t="str">
-        <v>0.02</v>
+        <v>TEST: RADIATION PROTECTION SURVEY REPORT</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>kV</v>
+      </c>
+      <c r="B44" t="str">
+        <v>mA</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Time</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Workload</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Location</v>
+      </c>
+      <c r="F44" t="str">
+        <v>mR/hr</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>TEST: RADIATION PROTECTION SURVEY REPORT</v>
+        <v>80</v>
+      </c>
+      <c r="B45" t="str">
+        <v>100</v>
+      </c>
+      <c r="C45" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="D45" t="str">
+        <v>500</v>
+      </c>
+      <c r="E45" t="str">
+        <v>Control Console (Operator Position)</v>
+      </c>
+      <c r="F45" t="str">
+        <v>0.02</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>kV</v>
+        <v>80</v>
       </c>
       <c r="B46" t="str">
-        <v>mA</v>
+        <v>100</v>
       </c>
       <c r="C46" t="str">
-        <v>Time</v>
+        <v>0.5</v>
       </c>
       <c r="D46" t="str">
-        <v>Workload</v>
+        <v>500</v>
       </c>
       <c r="E46" t="str">
-        <v>Location</v>
+        <v>Outside Patient Entrance Door</v>
       </c>
       <c r="F46" t="str">
-        <v>mR/hr</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v>80</v>
-      </c>
-      <c r="B47" t="str">
-        <v>100</v>
-      </c>
-      <c r="C47" t="str">
-        <v>0.5</v>
-      </c>
-      <c r="D47" t="str">
-        <v>500</v>
-      </c>
-      <c r="E47" t="str">
-        <v>Control Console (Operator Position)</v>
-      </c>
-      <c r="F47" t="str">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="str">
-        <v>80</v>
-      </c>
-      <c r="B48" t="str">
-        <v>100</v>
-      </c>
-      <c r="C48" t="str">
-        <v>0.5</v>
-      </c>
-      <c r="D48" t="str">
-        <v>500</v>
-      </c>
-      <c r="E48" t="str">
-        <v>Outside Patient Entrance Door</v>
-      </c>
-      <c r="F48" t="str">
         <v>0.01</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N48"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R46"/>
   </ignoredErrors>
 </worksheet>
 </file>